--- a/outputs/EG品質確認テスト_課題整理_20260630.xlsx
+++ b/outputs/EG品質確認テスト_課題整理_20260630.xlsx
@@ -13,7 +13,7 @@
     <sheet name="運転課題" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'課題マスタ'!$A$2:$K$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'課題マスタ'!$A$2:$K$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RD事前提出依頼'!$A$2:$G$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'スケジュール'!$A$2:$F$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'運転課題'!$A$2:$H$24</definedName>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>EG品質確認テスト(EG-1/EG-2) 課題整理  2026-06-30 C2定例反映</t>
+          <t>EG品質確認テスト(EG-1/EG-2) 課題整理（2026-06-30時点）</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>出典・備考</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>06-24対面レビューでは『テスト必要性は弱い・低水比論点は外す』、06-30デッキはEG-1/EG-2二本立て・濃縮を主課題と再提示で位置づけに揺れあり(要確認)</t>
+          <t>テストの位置づけに揺れあり(必要性は限定的との見方と、不純物濃縮を主課題にEG-1/EG-2の二本立てとする見方) (要確認)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>_20260630_原稿/C2定例_原稿 他 / 造語・程度語の言い切りを避け仮説駆動で統一(要確認)</t>
+          <t>造語・程度語の言い切りを避け仮説駆動で統一 (要確認)</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>既存モデルめやすではMEG HUV220が規格0.15を超える方向(0.2前後)。足元の原料EO由来高ALDは未織込で過大評価ぎみ＝幅を持って扱う。RDの詰め残しを事前提示要(要確認)</t>
+          <t>既存モデルめやすではMEG HUV220が規格0.15を超える方向(0.2前後)。足元の原料EO由来高ALDは未織込で過大評価ぎみ＝幅を持って扱う。RDの詰め残しを事前提示要 (要確認)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>必要性と制約_rev1.pptx 他 / RDで事前提示してほしいデータ=机上off-ramp判断の根拠一式</t>
+          <t>RDで事前提示してほしいデータ=机上off-ramp判断の根拠一式</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>C2宿題1 / MEG-DEG品質悪化_アルデヒド_UV_色相.md 他 / RD事前提示の最重要データ。前田指摘『はっきりしたデータはないはず』</t>
+          <t>RD事前提示の最重要データ。前田指摘『はっきりしたデータはないはず』</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>6/16-6/17議事二段解釈: DEG側=持込水分(数百ppm)による鎖伸長抑制説／MEG側=リン酸そのもののG-ALD抑制。採取は足場組み後(定修中)(要確認)</t>
+          <t>二段の解釈: DEG側=持込水分(数百ppm)による鎖伸長抑制説／MEG側=リン酸そのもののG-ALD抑制。採取は足場組み後(定修中) (要確認)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>EG着色仮説ABC_科学的検証_文献整理.md 他 / no3と一体。リン酸=Na3PO4</t>
+          <t>と一体。リン酸=Na3PO4</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>C2宿題2(前田チャット追加) / MEG-DEG品質悪化.md 他 / RD事前提示データ。各指標は自分の規格と照合</t>
+          <t>RD事前提示データ。各指標は自分の規格と照合</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>事実・仮説・対応の木村PMフォーマットで仮説1枚をデッキ新設しSAで示せる形に整理。RDベンチで再現性を確保。アセト×フォルム2Dマップで過去『単独高』運転OK領域とM50位置・対策ルートを示す</t>
+          <t>事実・仮説・対応の木村PMフォーマットで仮説1枚を資料新設しSAで示せる形に整理。RDベンチで再現性を確保。アセト×フォルム2Dマップで過去『単独高』運転OK領域とM50位置・対策ルートを示す</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>C2ラップアップ / MEG-DEG品質悪化.md 他 / 会議では深入りせず精査中とする。鉄サビは450nm主因でないが無罪と言い切らない(要確認)</t>
+          <t>会議では深入りせず精査中とする。鉄サビは450nm主因でないが無罪と言い切らない (要確認)</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>黒色付着物混入でUV上昇も450nmピーク再現せず。前田仮説=ポリエナールなら350から450シフトするが試験ではシフトしない、サビは原因でなく結果の可能性。C-1503付着物は主成分鉄・微量リン(要確認)</t>
+          <t>黒色付着物混入でUV上昇も450nmピーク再現せず。前田仮説=ポリエナールなら350から450シフトするが試験ではシフトしない、サビは原因でなく結果の可能性。C-1503付着物は主成分鉄・微量リン (要確認)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>EG着色仮説ABC.md 他 / 局所腐食・380nm寄与は無罪と言い切らない(要確認)</t>
+          <t>局所腐食・380nm寄与は無罪と言い切らない (要確認)</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>C2定例6/1論点 / MEG-DEG品質悪化.md / 要RD検証</t>
+          <t>要RD検証</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>計画説明_rev0.pptx / EG反応系R-1401.md 他 / AALDはHUV220の主因物質。no5の根拠データと連動</t>
+          <t>AALDはHUV220の主因物質。根拠データと連動</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>目標G-ALD≦2,500g/h・製品DEG UV330≦0.2・MEG塔底≦167℃。リン酸=Na3PO4。塔頂圧ダウンはGALD生成抑制(方案2)。167℃低温化はアセト/ホルム分解されず後段DEG移行のトレードオフあり(要確認)</t>
+          <t>目標G-ALD≦2,500g/h・製品DEG UV330≦0.2・MEG塔底≦167℃。リン酸=Na3PO4。塔頂圧ダウンはGALD生成抑制(方案2)。167℃低温化はアセト/ホルム分解されず後段DEG移行のトレードオフあり (要確認)</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>_20260630_原稿(S6) / 計画説明_rev0 / EG品質対応_PJ.md / テスト時はFALDパージ等入口低減を打たない</t>
+          <t>テスト時はFALDパージ等入口低減を打たない</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>計画説明_rev0 / MEG-DEG品質悪化.md 他 / DEG確定色相はテスト中に出ない(寝かせ1週間〜10日)、隔離隔離して寝かせる後段判定は別建て</t>
+          <t>DEG確定色相はテスト中に出ない(寝かせ1週間〜10日)、隔離隔離して寝かせる後段判定は別建て</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>MEG-DEG品質悪化.md / RDに早期判定指標の妥当性データ提示を依頼</t>
+          <t>RDに早期判定指標の妥当性データ提示を依頼</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>EG系薬剤添加_NaOHとリン酸Na.md 他 / RDにNaOHあり/なし比較データを依頼</t>
+          <t>RDにNaOHあり/なし比較データを依頼</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>C2宿題8 / EG反応系R-1401.md 他 / AALDに注力すべき(髙橋)</t>
+          <t>AALDに注力すべき(髙橋)</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>C2宿題7(藤本Q) / deck_edit_plan.md 他 / 平尾担当宿題。no18のEG-1評価方法に直結</t>
+          <t>EG-1評価方法に直結</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>_20260630_原稿(S11) / EG品質対応_PJ.md 他 / 二本立ての一方。MEGあたり量で見ればM50とほぼ同等まで再現の見立て</t>
+          <t>二本立ての一方。MEGあたり量で見ればM50とほぼ同等まで再現の見立て</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>_20260630_原稿(S12) / 計画説明_rev0 他 / 二本立ての他方。EG-2が濃度の高ALDを担当</t>
+          <t>二本立ての他方。EG-2が濃度の高ALDを担当</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>_20260630_原稿(S2) / 計画説明_rev0 他 / 反応器入口不純物約2.3倍濃縮が肝</t>
+          <t>反応器入口不純物約2.3倍濃縮が肝</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>EG反応系R-1401.md / EG品質対応_PJ.md(06-29) / 宿題9のスコープ分けと連動(要確認)</t>
+          <t>スコープ分けと連動 (要確認)</t>
         </is>
       </c>
     </row>
@@ -1639,11 +1639,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>EG反応系R-1401.md / EG品質対応_PJ.md</t>
-        </is>
-      </c>
+      <c r="K22" s="3" t="inlineStr"/>
     </row>
     <row r="23" ht="49" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -1696,7 +1692,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>水バイパス起業_DEG-TEG増産と反応モデル.md / M50ラボM/D/T=86/13.5/0.5未達と整合</t>
+          <t>M50ラボM/D/T=86/13.5/0.5未達と整合</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1747,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>C2宿題6(藤本Q) / 計画説明_rev0 / 触媒被毒_PJ.md / そこまでやっても将来条件にはまらない(木村)、外挿気味アウトプット</t>
+          <t>そこまでやっても将来条件にはまらない(木村)、外挿気味アウトプット</t>
         </is>
       </c>
     </row>
@@ -1804,11 +1800,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>EG低稼働テスト_PJ.md</t>
-        </is>
-      </c>
+      <c r="K25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="3" t="n">
@@ -1859,11 +1851,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>EG低稼働テスト_PJ.md</t>
-        </is>
-      </c>
+      <c r="K26" s="3" t="inlineStr"/>
     </row>
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -1916,7 +1904,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>計画説明_rev0 / EG反応系R-1401.md / 圧力ダウン・排水パージはアセト低減効果小、対策から外しホルム低減へ注力する案</t>
+          <t>圧力ダウン・排水パージはアセト低減効果小、対策から外しホルム低減へ注力する案</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1934,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>低稼働テスト(7/28〜8/2,6日): 外販EO300/MEG222/DEG84/TEG9 t/d。低水比テスト(8/3〜8/5,3日): 外販EO200/MEG338/DEG100/TEG9 t/d。日別バランス表(26年7月EG稼働テスト検討.xlsx)で管理</t>
+          <t>低稼働テスト(7/28〜8/2,6日): 外販EO300/MEG222/DEG84/TEG9 t/d。低水比テスト(8/3〜8/5,3日): 外販EO200/MEG338/DEG100/TEG9 t/d。日別バランス表で管理</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -1971,7 +1959,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>XLSX_26年7月EG稼働テスト検討.txt / XLSXが最新計画</t>
+          <t>XLSXが最新計画</t>
         </is>
       </c>
     </row>
@@ -1991,12 +1979,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>テスト条件EO稼働率の版間不整合(rev1=下限60%／6/24版=テスト50%)の確定</t>
+          <t>テスト条件のEO稼働率の確定(過去案の下限60%／現行テスト50%)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>60-62%だとMEG≈9.5t/hで目標7.3に届かず、50%でMEGリサイクル最大化しMEG≈7.5t/h=M50近傍。rev1は『EO稼働60%が下限』と旧版表記で版間不整合。HPEO0.86の50%ロード時妥当値(要確認)</t>
+          <t>60-62%だとMEG≈9.5t/hで目標7.3に届かず、50%でMEGリサイクル最大化しMEG≈7.5t/h=M50近傍。過去案は『EO稼働60%が下限』で現行50%と不整合 (要確認)</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -2006,7 +1994,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>デッキ全面更新時</t>
+          <t>資料更新時</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -2026,11 +2014,11 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>必要性と制約_rev1 / deck_edit_plan.md / 最新は50%だがrev1の60%表記は旧版(要確認)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1">
+          <t>最新は50%、過去案の60%は更新前 (要確認)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="n">
         <v>28</v>
       </c>
@@ -2081,7 +2069,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29_本田PJ_タンクバランス整理.md / 平尾フラグの残課題</t>
+          <t>平尾フラグの残課題</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2124,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>EG低稼働テスト_PJ.md / 計画説明_rev0 他 / 実効MAXの定義(8,265tの内訳とT-301/306扱い)が最大の感度点(要確認)</t>
+          <t>実効MAXの定義(8,265tの内訳とT-301/306扱い)が最大の感度点 (要確認)</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2149,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>T-305 Max880t、低稼働テスト中の外販EO抜出約300t/d想定で880÷300≒約3日で最初に効く。XLSXでは7/28〜8/2が300t/d、8/3〜8/5が200t/d。数字暫定(要確認)</t>
+          <t>T-305 Max880t、低稼働テスト中の外販EO抜出約300t/d想定で880÷300≒約3日で最初に効く。XLSXでは7/28〜8/2が300t/d、8/3〜8/5が200t/d。数字暫定 (要確認)</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -2191,7 +2179,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29_本田PJ_タンクバランス整理.md / XLSX / テスト中も通常出荷が回るかで滞留日数が変わる(要確認)</t>
+          <t>テスト中も通常出荷が回るかで滞留日数が変わる (要確認)</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2204,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>200tオフタンク容量確保が必要。テスト開始日は6/26想定(PJノート)だが06-30原稿では7月末〜8月頭で開始日確定要(要確認)</t>
+          <t>200tオフタンク容量確保が必要。テスト開始日は6/26想定だが7月末〜8月頭で開始日確定要 (要確認)</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -2244,13 +2232,9 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>EG低稼働テスト_PJ.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="34" customHeight="1">
+      <c r="K33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="n">
         <v>32</v>
       </c>
@@ -2271,7 +2255,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>DEGタンクは現状2基使用、3基目の戻り時期未確認。DEGタンク切り分け(no33)の前提条件</t>
+          <t>DEGタンクは現状2基使用、3基目の戻り時期未確認。DEGタンク切り分けの前提条件</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -2299,11 +2283,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>C2宿題4 / MEG-DEG品質悪化.md</t>
-        </is>
-      </c>
+      <c r="K34" s="3" t="inlineStr"/>
     </row>
     <row r="35" ht="49" customHeight="1">
       <c r="A35" s="3" t="n">
@@ -2356,7 +2336,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>C2宿題3 / MEG-DEG品質悪化.md / no32(3期DEGタンク戻り時期)が前提</t>
+          <t>(3期DEGタンク戻り時期)が前提</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2391,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>EG品質対応_PJ.md / 2026-06-15_朝会.md 他 / ベビー約300t。東レ=MEG文脈</t>
+          <t>ベビー約300t。東レ=MEG文脈</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2416,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>オファー段階で封印担保が可能かが課題。国際内航線向けは一回の容量に制約があり現在の数字では対応困難な可能性。ローリー/タグ運用の詳細要件は不明確(要確認)</t>
+          <t>オファー段階で封印担保が可能かが課題。国際内航線向けは一回の容量に制約があり現在の数字では対応困難な可能性。ローリー/タグ運用の詳細要件は不明確 (要確認)</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -2464,11 +2444,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15_朝会.md</t>
-        </is>
-      </c>
+      <c r="K37" s="3" t="inlineStr"/>
     </row>
     <row r="38" ht="49" customHeight="1">
       <c r="A38" s="3" t="n">
@@ -2521,7 +2497,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>C2木村コメント / 触媒被毒_PJ.md / 被毒の足元状態がテスト条件を律速(要確認)</t>
+          <t>被毒の足元状態がテスト条件を律速 (要確認)</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2552,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>C2髙橋コメント / 水添反応器R-1601転用_PlanD.md 他 / SK1BH=イオン交換樹脂。RDにIERでのアルデヒド増挙動データ提示を依頼</t>
+          <t>SK1BH=イオン交換樹脂。RDにIERでのアルデヒド増挙動データ提示を依頼</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2607,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>触媒被毒_PJ.md / C2髙橋コメント / no5のFALD/AALD推定根拠と連動</t>
+          <t>FALD/AALD推定根拠と連動</t>
         </is>
       </c>
     </row>
@@ -2684,11 +2660,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>EG系薬剤添加_NaOHとリン酸Na.md / EG品質対応_PJ.md</t>
-        </is>
-      </c>
+      <c r="K41" s="3" t="inlineStr"/>
     </row>
     <row r="42" ht="64" customHeight="1">
       <c r="A42" s="3" t="n">
@@ -2711,7 +2683,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>C-1501塔頂圧27から23kPaA・BTM167℃以下(実施済)でGALD/HUV抑制。E-1502凝縮能力が制約。167℃低温化は本来MEG塔で熱分解されるアセト/ホルムが分解されず後段DEGへ移行しHUV悪化を招きうる(トレードオフ)。温度低下は色相悪化を止めない可能性(要確認)</t>
+          <t>C-1501塔頂圧27から23kPaA・BTM167℃以下(実施済)でGALD/HUV抑制。E-1502凝縮能力が制約。167℃低温化は本来MEG塔で熱分解されるアセト/ホルムが分解されず後段DEGへ移行しHUV悪化を招きうる(トレードオフ)。温度低下は色相悪化を止めない可能性 (要確認)</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2741,7 +2713,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>MEG-DEG品質悪化.md / M50負荷1.5倍まで運転可能見込み。温度操作の因果は未解決</t>
+          <t>M50負荷1.5倍まで運転可能見込み。温度操作の因果は未解決</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2768,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>MEG-DEG品質悪化.md / C-1501_G-ALD生成分布.md / G-ALDはC-1501 TOPセクション充填物表面で約2/3生成。S/U後約1.5ヶ月で2000g/h到達(この低G-ALD期間を狙う)</t>
+          <t>G-ALDはC-1501 TOPセクション充填物表面で約2/3生成。S/U後約1.5ヶ月で2000g/h到達(この低G-ALD期間を狙う)</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2823,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>C-1501_G-ALD生成分布とAspenモデル.md / C-1504フィード流量は分配器最大設計1.75t/hで2.6から1.75是正が正</t>
+          <t>C-1504フィード流量は分配器最大設計1.75t/hで2.6から1.75是正が正</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2848,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>過去現場報告との齟齬が発生。要訂正報告。LERA由来仮置きは分析データなしで妥当性検証要(要確認)</t>
+          <t>過去現場報告との齟齬が発生。要訂正報告。LERA由来仮置きは分析データなしで妥当性検証要 (要確認)</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2906,7 +2878,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>EG反応系R-1401.md(6/26) / no5のFALD/AALD推定根拠の前提</t>
+          <t>FALD/AALD推定根拠の前提</t>
         </is>
       </c>
     </row>
@@ -2959,11 +2931,7 @@
           <t>低</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>EG反応系R-1401.md(6/26)</t>
-        </is>
-      </c>
+      <c r="K46" s="3" t="inlineStr"/>
     </row>
     <row r="47" ht="49" customHeight="1">
       <c r="A47" s="3" t="n">
@@ -3014,11 +2982,7 @@
           <t>低</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>EG反応系R-1401.md(6/29)</t>
-        </is>
-      </c>
+      <c r="K47" s="3" t="inlineStr"/>
     </row>
     <row r="48" ht="49" customHeight="1">
       <c r="A48" s="3" t="n">
@@ -3071,7 +3035,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>EG反応系R-1401.md(6/29) / 修正ログB群と整合(一般化工指標で組み直し)</t>
+          <t>修正ログB群と整合(一般化工指標で組み直し)</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3060,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>RB側補償項目が未整理で入口対応との関係が不明確。3次SAオーダー前に品質観点を優先。『RB』『RG』略号は文脈不明(要確認)</t>
+          <t>RB側補償項目が未整理で入口対応との関係が不明確。3次SAオーダー前に品質観点を優先。『RB』『RG』略号は文脈不明 (要確認)</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -3124,11 +3088,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15_朝会.md</t>
-        </is>
-      </c>
+      <c r="K49" s="3" t="inlineStr"/>
     </row>
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="3" t="n">
@@ -3179,11 +3139,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-12_DEG対策会議.md</t>
-        </is>
-      </c>
+      <c r="K50" s="3" t="inlineStr"/>
     </row>
     <row r="51" ht="49" customHeight="1">
       <c r="A51" s="3" t="n">
@@ -3234,11 +3190,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-12_DEG対策会議.md / 2026-06-15_朝会.md</t>
-        </is>
-      </c>
+      <c r="K51" s="3" t="inlineStr"/>
     </row>
     <row r="52" ht="49" customHeight="1">
       <c r="A52" s="3" t="n">
@@ -3291,7 +3243,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>MEG-DEG品質悪化.md / no11,12と連動</t>
+          <t>,12と連動</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3298,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>EG反応系R-1401.md / 平尾アクション=SAでA-ALDパージのK影響評価</t>
+          <t>平尾アクション=SAでA-ALDパージのK影響評価</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3353,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>EG濃縮系_三重効用缶の運転不安定性と腐食.md / BDI実績(C-1401 economy≒2.95)が基準。水比6まで濃縮との整合は要確認</t>
+          <t>BDI実績(C-1401 economy≒2.95)が基準。水比6まで濃縮との整合は要確認</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3408,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>コンデンサ能力評価_汚れ係数とM50負荷.md / M50機器実績評価.md / 循環水低下リスク(密度差駆動力喪失)が最大懸念。low confidence</t>
+          <t>循環水低下リスク(密度差駆動力喪失)が最大懸念。low confidence</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3463,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>M50機器実績評価_OPERATION_RANGE.md / EG反応系R-1401.md / 8月末MEC見積仕様確定と整合</t>
+          <t>8月末MEC見積仕様確定と整合</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3518,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>M50ダウンサイジング_PJ.md / 計画と判定とテスト代替仮説.md / no52と一体</t>
+          <t>と一体</t>
         </is>
       </c>
     </row>
@@ -3619,11 +3571,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>水添反応器R-1601転用_PlanD.md</t>
-        </is>
-      </c>
+      <c r="K58" s="3" t="inlineStr"/>
     </row>
     <row r="59" ht="34" customHeight="1">
       <c r="A59" s="3" t="n">
@@ -3674,11 +3622,7 @@
           <t>低</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>水添反応器R-1601転用_PlanD.md / PLAUD 2026-03-11</t>
-        </is>
-      </c>
+      <c r="K59" s="3" t="inlineStr"/>
     </row>
     <row r="60" ht="34" customHeight="1">
       <c r="A60" s="3" t="n">
@@ -3731,7 +3675,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>水添反応器R-1601転用_PlanD.md / 過去トラブルは対策済みと結論</t>
+          <t>過去トラブルは対策済みと結論</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3730,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>水バイパス起業_ポンプ故障教訓.md / 2025/6-12事例</t>
+          <t>2025/6-12事例</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3785,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>EG反応系R-1401.md / 引き継ぎ書_ALDバランスExcel評価.md / no51のV-1402圧低減が効くか不明に直結</t>
+          <t>V-1402圧低減が効くか不明に直結</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3840,7 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>EO精製塔性能評価テスト_REV.3.pptx / EG品質確認テストとは別テスト(3月トライ系制約)</t>
+          <t>EG品質確認テストとは別テスト(3月トライ系制約)</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3895,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12_DEG対策会議とストレーナー.md / 出荷ラインの色相悪化品・異物除去はテスト期間中品質確保と関係</t>
+          <t>出荷ラインの色相悪化品・異物除去はテスト期間中品質確保と関係</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3920,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>EO精製塔性能評価テスト(MEG低需要対応)REV.3は課1次SAチェックリスト全17項目該当4・未了0で確認完了済。EG関係はSA前・コンセプト固め段階</t>
+          <t>EO精製塔性能評価テスト(MEG低需要対応)は課1次SAチェックリスト全17項目該当4・未了0で確認完了済。EG関係はSA前・コンセプト固め段階</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -4006,7 +3950,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>EO精製塔性能評価テスト_REV.3.pptx / C2菱コメント / 菱コメント(出せる状態のテストか確認せよ、園さん指令)と整合</t>
+          <t>菱コメント(出せる状態のテストか確認せよ、園さん指令)と整合</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4005,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>C2菱Q・木村A / M50ダウンサイジング_PJ.md / SAが計画織込みの前提</t>
+          <t>SAが計画織込みの前提</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4030,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>EO稼働50%・MEG生産量を将来想定7.3近くまで下げる運転はSOP規定の運転条件範囲を外れ変更管理対象(6区分3.該当の可能性)。IL・安全弁設定・防護層が不変なら本質安全変更に直接は該当しない切り分け。課SA止まりか部SAかは別紙4で確定要(要確認)</t>
+          <t>EO稼働50%・MEG生産量を将来想定7.3近くまで下げる運転はSOP規定の運転条件範囲を外れ変更管理対象(6区分3.該当の可能性)。IL・安全弁設定・防護層が不変なら本質安全変更に直接は該当しない切り分け。課SA止まりか部SAかは別紙4で確定要 (要確認)</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -4114,11 +4058,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>変更管理_SA検討会_進め方と必要評価.md</t>
-        </is>
-      </c>
+      <c r="K67" s="3" t="inlineStr"/>
     </row>
     <row r="68" ht="49" customHeight="1">
       <c r="A68" s="3" t="n">
@@ -4141,7 +4081,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>プロセス本質安全に関わる変更・設計根拠/過去変更経緯が不明確な場合は部SA。50百万円以上はTTA(様式5-2)。リン酸塩添加・塔頂圧変更が本質安全に関わるか要判断。課SA止まりか部1次SAまで要るかは別紙4で確定(要確認)</t>
+          <t>プロセス本質安全に関わる変更・設計根拠/過去変更経緯が不明確な場合は部SA。50百万円以上はTTA(様式5-2)。リン酸塩添加・塔頂圧変更が本質安全に関わるか要判断。課SA止まりか部1次SAまで要るかは別紙4で確定 (要確認)</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -4171,7 +4111,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>変更管理_SA検討会_進め方と必要評価.md / 部SA最終承認は本田忍(保安/SA承認文脈)</t>
+          <t>部SA最終承認は本田忍(保安/SA承認文脈)</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4166,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>EG低稼働テスト_PJ.md / EG品質対応_PJ.md / 3次SA前にSOPレビュー要。竹中氏ヒアリング段取り(要確認)</t>
+          <t>3次SA前にSOPレビュー要。竹中氏ヒアリング段取り (要確認)</t>
         </is>
       </c>
     </row>
@@ -4279,11 +4219,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>触媒被毒_PJ.md / EG品質確認テスト概要</t>
-        </is>
-      </c>
+      <c r="K70" s="3" t="inlineStr"/>
     </row>
     <row r="71" ht="49" customHeight="1">
       <c r="A71" s="3" t="n">
@@ -4334,11 +4270,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>deck_edit_plan.md</t>
-        </is>
-      </c>
+      <c r="K71" s="3" t="inlineStr"/>
     </row>
     <row r="72" ht="34" customHeight="1">
       <c r="A72" s="3" t="n">
@@ -4391,7 +4323,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>EG反応系R-1401.md(6/29) / EG関係SAは織込みづらい(菱コメントと整合)</t>
+          <t>EG関係SAは織込みづらい(菱コメントと整合)</t>
         </is>
       </c>
     </row>
@@ -4444,11 +4376,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>C2宿題5(前田)</t>
-        </is>
-      </c>
+      <c r="K73" s="3" t="inlineStr"/>
     </row>
     <row r="74" ht="34" customHeight="1">
       <c r="A74" s="3" t="n">
@@ -4499,11 +4427,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15_朝会.md / 2026-06-12_DEG対策会議.md</t>
-        </is>
-      </c>
+      <c r="K74" s="3" t="inlineStr"/>
     </row>
     <row r="75" ht="49" customHeight="1">
       <c r="A75" s="3" t="n">
@@ -4554,68 +4478,64 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>EG品質対応_PJ.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="19" customHeight="1">
+      <c r="K75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="49" customHeight="1">
       <c r="A76" s="3" t="n">
         <v>74</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>会議</t>
+          <t>推進その他</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>事業部調整</t>
+          <t>スコープ</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>議事録作成方針の改善(結果だけでなく議論の背景・考え方・仮説・手順を残す)</t>
+          <t>EG-2起点にM50(8/20ゲート)と税群DEG品質対応のスコープ分け整理</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>社長(蟹部長/鈴木さん)指摘。タンクのpH管理関連も同時論点</t>
+          <t>基礎研リソース2人減・新人テーマ減で両立が厳しい。木村『AALD減らせない』とRD『AALD減らさないと』でストーリーずれ、AALDに注力すべき(髙橋)</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>今後の議事録は具体的データ・仮説・検討手順を含めて再整理。テスト関連の論点・仮説・手順を記録に残す</t>
+          <t>EG-2を起点にM50(8/20ゲート)向け対応と税群(DEG)品質対応のスコープを分けて整理。機器側はOPERATION RANGE整理、8月末機器更新評価へ集約。AALD注力(出口戦略=IER)とFALDパージ(方案3,期待薄)の重点を整理</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
+          <t>8/20ゲート/EG-2起点</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>木村/髙橋</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>木村/平尾</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>EG反応系R-1401.md(6/29)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="49" customHeight="1">
+          <t>,38,76と連動</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="34" customHeight="1">
       <c r="A77" s="3" t="n">
         <v>75</v>
       </c>
@@ -4626,32 +4546,32 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>スコープ</t>
+          <t>リソース</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>EG-2起点にM50(8/20ゲート)と税群DEG品質対応のスコープ分け整理</t>
+          <t>基礎研の出口戦略(水添/DEG IER)リソース確保の事業部・RT上位調整</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>基礎研リソース2人減・新人テーマ減で両立が厳しい。木村『AALD減らせない』とRD『AALD減らさないと』でストーリーずれ、AALDに注力すべき(髙橋)</t>
+          <t>基礎研リソース2人減・新人テーマ減で厳しい。出口戦略はリソース課題でM50スコープ分けと一体。IERでアルデヒド増の裏付けデータの位置づけ整理も要 (要確認)</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>EG-2を起点にM50(8/20ゲート)向け対応と税群(DEG)品質対応のスコープを分けて整理。機器側はOPERATION RANGE整理、8月末機器更新評価へ集約。AALD注力(出口戦略=IER)とFALDパージ(方案3,期待薄)の重点を整理</t>
+          <t>基礎研の出口戦略(製品DEGへのIER等)リソース確保を事業部・RT上位と調整する</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>8/20ゲート/EG-2起点</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>木村/髙橋</t>
+          <t>木村</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -4664,13 +4584,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>C2宿題9(髙橋) / M50機器実績評価.md 他 / no37,38,76と連動</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="34" customHeight="1">
+      <c r="K77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78" ht="49" customHeight="1">
       <c r="A78" s="3" t="n">
         <v>76</v>
       </c>
@@ -4681,51 +4597,51 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>リソース</t>
+          <t>スコープ</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>基礎研の出口戦略(水添/DEG IER)リソース確保の事業部・RT上位調整</t>
+          <t>プラントテストのM100/M50段階化(EBテスト)とテスト間の優先順序整理</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>基礎研リソース2人減・新人テーマ減で厳しい。出口戦略はリソース課題でM50スコープ分けと一体。IERでアルデヒド増の裏付けデータの位置づけ整理も要(要確認)</t>
+          <t>M50ではEO中検出下限以下で評価困難・切れない条件での本試験は現時点で危険・不可。第2段階はリアクターバイパスが増えるため特定運転点を検討</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>基礎研の出口戦略(製品DEGへのIER等)リソース確保を事業部・RT上位と調整する</t>
+          <t>第1段階(M100条件・抜き出し比率0.64)で分離性能・能力を1日程度で評価、第2段階(M50条件・抜き出し比率0.82)はM100で能力確認後に実施。中間タンク在庫を調整。EO吸収中削減は高稼働期8月・CO2循環系は低稼働期</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
+          <t>7月末(EBテスト)</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>木村/製造</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>木村</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>C2宿題10(髙橋) / 水添反応器R-1601転用_PlanD.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="49" customHeight="1">
+          <t>回収率の観点からM50で確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="34" customHeight="1">
       <c r="A79" s="3" t="n">
         <v>77</v>
       </c>
@@ -4736,32 +4652,32 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>スコープ</t>
+          <t>リソース</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>プラントテストのM100/M50段階化(EBテスト)とテスト間の優先順序整理</t>
+          <t>熱交換器クリーニング見積りの根拠整理とバックチェック・補助金企画</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>M50ではEO中検出下限以下で評価困難・切れない条件での本試験は現時点で危険・不可。第2段階はリアクターバイパスが増えるため特定運転点を検討</t>
+          <t>クリーニング見積りは51/15/15/18程度をざっくり算出(数値暫定)。『VC』の意味は不明(要確認)。テスト本体への直接関与は弱い周辺案件</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>第1段階(M100条件・抜き出し比率0.64)で分離性能・能力を1日程度で評価、第2段階(M50条件・抜き出し比率0.82)はM100で能力確認後に実施。中間タンク在庫を調整。EO吸収中削減は高稼働期8月・CO2循環系は低稼働期</t>
+          <t>見積り根拠を整理しバックチェック、優先度を確定。補助金対象の企画は31年タイミングで相談</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>7月末(EBテスト)</t>
+          <t>来週相談予定</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>木村/製造</t>
+          <t>平尾</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4771,14 +4687,10 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>EG反応系R-1401.md(6/29) / 回収率の観点からM50で確認</t>
-        </is>
-      </c>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr"/>
     </row>
     <row r="80" ht="49" customHeight="1">
       <c r="A80" s="3" t="n">
@@ -4791,37 +4703,37 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>スコープ</t>
+          <t>RD検証</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>デッキ全体トーンを断定回避・仮説駆動に統一しスライド前提ズレを是正</t>
+          <t>Shell RCA(触媒被毒原因)確定と事業継続性のShell正式確認(テスト/M50の事業前提)</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>指示文の『98枚』『スライド番号』が本フォルダのどのpptxとも不一致(編集計画の前提ズレ)。AI痕跡・外部引用・色付き装飾・、記号・造語・程度語の言い切りを使わない(ルール正本)。配布ファイル/番号体系は平尾確認待ち(要確認)</t>
+          <t>Shell RCA=触媒分析で鉄が全体的に存在・助触媒流出・液体水被毒が主要因と推定。Shell仮説(S/U時凝縮)とMCC仮説(定修中発錆)で時系列パス未統一。1年運転継続可否はM50/テスト全体の事業前提に関わる</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>全スライドで『こういう仮説に基づくと、こういうテストをしてもいいのでは』『対策は分かっている、テストで確認したい』の言い回しに統一。指示の論点名、本デッキ実スライド番号で対応付け。優先3-5枚=2Dマップ作替・制約全面更新・新規反応機構1枚・新規生産バランス1枚</t>
+          <t>Shell正式見解を要求(事業部)。6/22-7/3連日対策会議で原因究明を継続。現状触媒で1年運転継続可否/安全性をShellに確認</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>配布前/改訂時</t>
+          <t>対策会議6/22-7/3 Shell RCA回収</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>平尾/木村</t>
+          <t>石塚/事業部/Brayden(Shell)</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>要</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -4831,47 +4743,47 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>deck_edit_plan.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="34" customHeight="1">
+          <t>テスト時期7月末とS/U見込み7/11・触媒交換完了の整合 (要確認)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="49" customHeight="1">
       <c r="A81" s="3" t="n">
         <v>79</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>推進その他</t>
+          <t>設備</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>リソース</t>
+          <t>設備</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>熱交換器クリーニング見積りの根拠整理とバックチェック・補助金企画</t>
+          <t>触媒交換完了・S/U見込み(7/11)とテスト時期(7月末)の工程整合</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>クリーニング見積りは51/15/15/18程度をざっくり算出(数値暫定)。『VC』の意味は不明(要確認)。テスト本体への直接関与は弱い周辺案件</t>
+          <t>触媒抜出固着で難航しS/U見込み7/11(EOスタート)。R-1101A/Bの触媒充填・パージ・差圧測定が進行中。再発防止(泡検知器・DCS/IL改造・SIS I/L化は冬定修2027/1)。『キャンペーン』と言わず触媒交換</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>見積り根拠を整理しバックチェック、優先度を確定。補助金対象の企画は31年タイミングで相談</t>
+          <t>触媒交換・再発防止工事完了後にS/U、その後7月末にEG品質確認テスト。S/U手順は水持ち込まない方向に見直し(Shell推奨対策3)。S/Uからテストまでの立上げ調整スケジュールを確定</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>来週相談予定</t>
+          <t>S/U見込み7/11 テスト7月末</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>平尾</t>
+          <t>EOG技術/EO課/松井</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
@@ -4881,12 +4793,12 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15_朝会.md</t>
+          <t>7/11 S/Uからテスト7月末までの立上げ調整 (要確認)</t>
         </is>
       </c>
     </row>
@@ -4896,52 +4808,52 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>推進その他</t>
+          <t>運転</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>RD検証</t>
+          <t>プロセス</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Shell RCA(触媒被毒原因)確定と事業継続性のShell正式確認(テスト/M50の事業前提)</t>
+          <t>試運転(2025/4-5)でのTEG生産見込み大幅未達の知見(EG-1/EG-2評価の先行知見)</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Shell RCA=触媒分析で鉄が全体的に存在・助触媒流出・液体水被毒が主要因と推定。Shell仮説(S/U時凝縮)とMCC仮説(定修中発錆)で時系列パス未統一。1年運転継続可否はM50/テスト全体の事業前提に関わる</t>
+          <t>Step4 36t/hでEO+DEG、TEGが想定以上に低速。DEGリサイクルする製品ポートフォリオには影響しない。蒸気削減は対計画87%。T-ALD一時検出(&lt;1ppm)は水バイパス影響低い(木村判断)</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Shell正式見解を要求(事業部)。6/22-7/3連日対策会議で原因究明を継続。現状触媒で1年運転継続可否/安全性をShellに確認</t>
+          <t>DEG濃度低領域(DEGリサイクル無)で反応パラメータがずれるとの木村見解を踏まえEG評価へ反映。Step5でDEGリサイクル0.8t/h追加＋水バイパス40t/hで計画達成の経緯を参照</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>対策会議6/22-7/3 / Shell RCA回収</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>石塚/事業部/Brayden(Shell)</t>
+          <t>木村</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>要</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>触媒被毒_選択率低下対応_PJ.md / テスト時期7月末とS/U見込み7/11・触媒交換完了の整合(要確認)</t>
+          <t>EG-1/EG-2の評価方法・運転調整の先行知見</t>
         </is>
       </c>
     </row>
@@ -4951,37 +4863,37 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>設備</t>
+          <t>会議</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>設備</t>
+          <t>変更管理</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>触媒交換完了・S/U見込み(7/11)とテスト時期(7月末)の工程整合</t>
+          <t>立ち上げ方針(オンスペック最優先・包括的対策を先行し、事後フェーズでメカ特定と基準整備)の2段階枠組み</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>触媒抜出固着で難航しS/U見込み7/11(EOスタート)。R-1101A/Bの触媒充填・パージ・差圧測定が進行中。再発防止(泡検知器・DCS/IL改造・SIS I/L化は冬定修2027/1)。『キャンペーン』と言わず触媒交換</t>
+          <t>リン酸=リン酸ナトリウム(Na3PO4)。木村PM主導枠組み(6/26)</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>触媒交換・再発防止工事完了後にS/U、その後7月末にEG品質確認テスト。S/U手順は水持ち込まない方向に見直し(Shell推奨対策3)。S/Uからテストまでの立上げ調整スケジュールを確定</t>
+          <t>安全サイド評価で最悪条件を含む保守的見積もりで『やるべき対策』を明示。原料水由来循環量増加下で『濃度が下がる』方向の評価は危険として避ける。対策不要へ短絡する前提(消費ゼロ・循環影響無視・低濃度楽観)を避ける</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>S/U見込み7/11 / テスト7月末</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>EOG技術/EO課/松井</t>
+          <t>木村/平尾</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -4991,127 +4903,17 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>触媒被毒_選択率低下対応_PJ.md / 7/11 S/Uからテスト7月末までの立上げ調整(要確認)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="49" customHeight="1">
-      <c r="A84" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>運転</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>プロセス</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>試運転(2025/4-5)でのTEG生産見込み大幅未達の知見(EG-1/EG-2評価の先行知見)</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>Step4 36t/hでEO+DEG、TEGが想定以上に低速。DEGリサイクルする製品ポートフォリオには影響しない。蒸気削減は対計画87%。T-ALD一時検出(&lt;1ppm)は水バイパス影響低い(木村判断)</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>DEG濃度低領域(DEGリサイクル無)で反応パラメータがずれるとの木村見解を踏まえEG評価へ反映。Step5でDEGリサイクル0.8t/h追加＋水バイパス40t/hで計画達成の経緯を参照</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>木村</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>水バイパス起業_DEG-TEG増産と反応モデル.md / EG-1/EG-2の評価方法・運転調整の先行知見</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="49" customHeight="1">
-      <c r="A85" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>会議</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>変更管理</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>立ち上げ方針(オンスペック最優先・包括的対策を先行し、事後フェーズでメカ特定と基準整備)の2段階枠組み</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>リン酸=リン酸ナトリウム(Na3PO4)。木村PM主導枠組み(6/26)</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>安全サイド評価で最悪条件を含む保守的見積もりで『やるべき対策』を明示。原料水由来循環量増加下で『濃度が下がる』方向の評価は危険として避ける。対策不要へ短絡する前提(消費ゼロ・循環影響無視・低濃度楽観)を避ける</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>木村/平尾</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>EG反応系R-1401.md / no2のoff-ramp判断の枠組みと連動</t>
+          <t>off-ramp判断の枠組みと連動</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K85"/>
+  <autoFilter ref="A2:K83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5334,7 +5136,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>事実・仮説・対応の木村PMフォーマットで仮説1枚をデッキ新設しSAで示せる形に整理。RDベンチで再現性を確保。アセト×フォルム2Dマップで過去『単独高』運転OK領域とM50位置・対策ルートを示す</t>
+          <t>事実・仮説・対応の木村PMフォーマットで仮説1枚を資料新設しSAで示せる形に整理。RDベンチで再現性を確保。アセト×フォルム2Dマップで過去『単独高』運転OK領域とM50位置・対策ルートを示す</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -6144,7 +5946,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>対策会議6/22-7/3 / Shell RCA回収</t>
+          <t>対策会議6/22-7/3 Shell RCA回収</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -6241,7 +6043,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>06-24対面レビューと06-30デッキの位置づけの揺れを解消(要確認)</t>
+          <t>テストの位置づけの揺れを解消 (要確認)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -6276,7 +6078,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>S/Uからテスト7月末までの立上げ調整スケジュール確定要(要確認)</t>
+          <t>S/Uからテスト7月末までの立上げ調整スケジュール確定要 (要確認)</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6103,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>外販EOタンク2基(T-301/T-306)使用不可・お盆8/17在庫ピーク約6,293t。前倒し不可で7/5成立。実効MAX定義が感度点(要確認)</t>
+          <t>外販EOタンク2基(T-301/T-306)使用不可・お盆8/17在庫ピーク約6,293t。前倒し不可で7/5成立。実効MAX定義が感度点 (要確認)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -7195,7 +6997,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>低稼働テスト(7/28〜8/2,6日): 外販EO300/MEG222/DEG84/TEG9 t/d。低水比テスト(8/3〜8/5,3日): 外販EO200/MEG338/DEG100/TEG9 t/d。日別バランス表(26年7月EG稼働テスト検討.xlsx)で管理</t>
+          <t>低稼働テスト(7/28〜8/2,6日): 外販EO300/MEG222/DEG84/TEG9 t/d。低水比テスト(8/3〜8/5,3日): 外販EO200/MEG338/DEG100/TEG9 t/d。日別バランス表で管理</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -7225,12 +7027,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>テスト条件EO稼働率の版間不整合(rev1=下限60%／6/24版=テスト50%)の確定</t>
+          <t>テスト条件のEO稼働率の確定(過去案の下限60%／現行テスト50%)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>60-62%だとMEG≈9.5t/hで目標7.3に届かず、50%でMEGリサイクル最大化しMEG≈7.5t/h=M50近傍。rev1は『EO稼働60%が下限』と旧版表記で版間不整合。HPEO0.86の50%ロード時妥当値(要確認)</t>
+          <t>60-62%だとMEG≈9.5t/hで目標7.3に届かず、50%でMEGリサイクル最大化しMEG≈7.5t/h=M50近傍。過去案は『EO稼働60%が下限』で現行50%と不整合 (要確認)</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -7240,7 +7042,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>デッキ全面更新時</t>
+          <t>資料更新時</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -7350,7 +7152,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>T-305 Max880t、低稼働テスト中の外販EO抜出約300t/d想定で880÷300≒約3日で最初に効く。XLSXでは7/28〜8/2が300t/d、8/3〜8/5が200t/d。数字暫定(要確認)</t>
+          <t>T-305 Max880t、低稼働テスト中の外販EO抜出約300t/d想定で880÷300≒約3日で最初に効く。XLSXでは7/28〜8/2が300t/d、8/3〜8/5が200t/d。数字暫定 (要確認)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -7390,7 +7192,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>200tオフタンク容量確保が必要。テスト開始日は6/26想定(PJノート)だが06-30原稿では7月末〜8月頭で開始日確定要(要確認)</t>
+          <t>200tオフタンク容量確保が必要。テスト開始日は6/26想定だが7月末〜8月頭で開始日確定要 (要確認)</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -7414,7 +7216,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
+    <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="n">
         <v>17</v>
       </c>
@@ -7430,7 +7232,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>DEGタンクは現状2基使用、3基目の戻り時期未確認。DEGタンク切り分け(no33)の前提条件</t>
+          <t>DEGタンクは現状2基使用、3基目の戻り時期未確認。DEGタンク切り分けの前提条件</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -7550,7 +7352,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>オファー段階で封印担保が可能かが課題。国際内航線向けは一回の容量に制約があり現在の数字では対応困難な可能性。ローリー/タグ運用の詳細要件は不明確(要確認)</t>
+          <t>オファー段階で封印担保が可能かが課題。国際内航線向けは一回の容量に制約があり現在の数字では対応困難な可能性。ローリー/タグ運用の詳細要件は不明確 (要確認)</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
